--- a/accessories/cable-2/cable-2.xlsx
+++ b/accessories/cable-2/cable-2.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\adowney2\Documents\GitHub\Battery-Lab-Hardware\accessories\cable-2\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/4c0fa0fe96562a9e/Documents/GitHub/Battery-Lab-Hardware/accessories/cable-2/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8D074E32-F380-4A8B-BFB4-C9C0509B5722}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="56" documentId="13_ncr:1_{8D074E32-F380-4A8B-BFB4-C9C0509B5722}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BC190208-072E-41E2-B21D-04C696366BAB}"/>
   <bookViews>
-    <workbookView xWindow="-16320" yWindow="-6540" windowWidth="16440" windowHeight="28320" xr2:uid="{FDAE7DA4-9528-4FC7-A320-70DA50473DCE}"/>
+    <workbookView xWindow="15480" yWindow="1080" windowWidth="3720" windowHeight="5527" xr2:uid="{FDAE7DA4-9528-4FC7-A320-70DA50473DCE}"/>
   </bookViews>
   <sheets>
     <sheet name="bill_of_materials" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="82" uniqueCount="80">
   <si>
     <t>Individual Cost</t>
   </si>
@@ -216,6 +216,66 @@
   </si>
   <si>
     <t>Q5-2X-3/4-01-QB48IN-5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SB50/120 T Handle </t>
+  </si>
+  <si>
+    <t>Connector T Handle For SBS® 50, SBS® 75X Series</t>
+  </si>
+  <si>
+    <t>113899P1</t>
+  </si>
+  <si>
+    <t>https://www.digikey.com/en/products/detail/anderson-power-products-inc/113899P1/10647423?s=N4IgTCBcDaIIxwMwA4CcqAKcQF0C%2BQA</t>
+  </si>
+  <si>
+    <t>HDW.BAG FOR SB/SBS50-HDL</t>
+  </si>
+  <si>
+    <t>104G17</t>
+  </si>
+  <si>
+    <t>https://www.digikey.com/en/products/detail/anderson-power-products-inc/104G17/14552097</t>
+  </si>
+  <si>
+    <t>SB50 Handle Screws</t>
+  </si>
+  <si>
+    <t>Standard Socket Head Cap Screw: M3x0.50, 20 mm Lg, Low-Profile Std, Black Oxide, Alloy Steel, 50 PK</t>
+  </si>
+  <si>
+    <t>LHS4803020-050P1</t>
+  </si>
+  <si>
+    <t>https://www.grainger.com/product/Standard-Socket-Head-Cap-Screw-6EA45</t>
+  </si>
+  <si>
+    <t>T Handle Hex Nut</t>
+  </si>
+  <si>
+    <t>Hex Nut: Std Hex, M3x0.50 Thread, 5.5 mm Hex Wd, 2.4 mm Hex Ht, Steel, Class 8, Zinc-Plated, 100 PK</t>
+  </si>
+  <si>
+    <t>M01300.030.0001</t>
+  </si>
+  <si>
+    <t>https://www.grainger.com/product/Hex-Nut-Std-Hex-26KR85?searchQuery=M01300.030.0001&amp;searchBar=true&amp;tier=Tier+6&amp;suggestConfigId=6&amp;s_e=false</t>
+  </si>
+  <si>
+    <t>SBS75 Handle Screws Long</t>
+  </si>
+  <si>
+    <t>SBS75 Handle Screws Short</t>
+  </si>
+  <si>
+    <t>Standard Socket Head Cap Screw: M3x0.50, 18 mm Lg, Std, Black Oxide, Alloy Steel, Class 12.9, 100 PK</t>
+  </si>
+  <si>
+    <t>M07000.030.0018</t>
+  </si>
+  <si>
+    <t>https://www.grainger.com/product/Standard-Socket-Head-Cap-Screw-6CE54</t>
   </si>
 </sst>
 </file>
@@ -228,7 +288,7 @@
     <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0.00"/>
     <numFmt numFmtId="165" formatCode="\$#,##0.00"/>
   </numFmts>
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -274,6 +334,12 @@
       <name val="Arial"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -307,7 +373,7 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -355,6 +421,12 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+      <alignment vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="4">
@@ -697,7 +769,7 @@
   <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="22.28515625" customWidth="1"/>
-    <col min="2" max="2" width="37.85546875" customWidth="1"/>
+    <col min="2" max="2" width="40.5703125" customWidth="1"/>
     <col min="3" max="3" width="20.7109375" customWidth="1"/>
     <col min="4" max="4" width="15.85546875" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="13.5703125" bestFit="1" customWidth="1"/>
@@ -1049,59 +1121,129 @@
       <c r="I12" s="4"/>
     </row>
     <row r="13" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="10"/>
-      <c r="B13" s="2"/>
-      <c r="C13" s="2"/>
-      <c r="D13" s="2"/>
-      <c r="E13" s="9"/>
-      <c r="F13" s="9"/>
+      <c r="A13" s="10" t="s">
+        <v>60</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="D13" s="2">
+        <v>1</v>
+      </c>
+      <c r="E13" s="8">
+        <v>2.72</v>
+      </c>
+      <c r="F13" s="9">
+        <v>2.72</v>
+      </c>
       <c r="G13" s="5"/>
-      <c r="H13" s="1"/>
+      <c r="H13" s="3" t="s">
+        <v>63</v>
+      </c>
       <c r="I13" s="4"/>
     </row>
     <row r="14" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="10"/>
-      <c r="B14" s="2"/>
-      <c r="C14" s="4"/>
-      <c r="D14" s="2"/>
-      <c r="E14" s="9"/>
-      <c r="F14" s="9"/>
+      <c r="A14" s="10" t="s">
+        <v>67</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="C14" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="D14" s="2">
+        <v>2</v>
+      </c>
+      <c r="E14" s="9">
+        <v>1.97</v>
+      </c>
+      <c r="F14" s="9">
+        <v>3.94</v>
+      </c>
       <c r="G14" s="5"/>
-      <c r="H14" s="1"/>
+      <c r="H14" s="1" t="s">
+        <v>66</v>
+      </c>
       <c r="I14" s="4"/>
     </row>
     <row r="15" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="10"/>
-      <c r="B15" s="2"/>
-      <c r="C15" s="2"/>
-      <c r="D15" s="2"/>
-      <c r="E15" s="8"/>
-      <c r="F15" s="9"/>
+      <c r="A15" s="10" t="s">
+        <v>75</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="D15" s="2">
+        <v>2</v>
+      </c>
+      <c r="E15" s="8">
+        <v>0.37</v>
+      </c>
+      <c r="F15" s="9">
+        <v>0.74</v>
+      </c>
       <c r="G15" s="5"/>
-      <c r="H15" s="3"/>
+      <c r="H15" s="3" t="s">
+        <v>70</v>
+      </c>
       <c r="I15" s="4"/>
     </row>
     <row r="16" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="11"/>
-      <c r="B16" s="11"/>
-      <c r="C16" s="11"/>
-      <c r="D16" s="12"/>
-      <c r="E16" s="13"/>
-      <c r="F16" s="9"/>
+      <c r="A16" s="10" t="s">
+        <v>76</v>
+      </c>
+      <c r="B16" s="11" t="s">
+        <v>77</v>
+      </c>
+      <c r="C16" s="11" t="s">
+        <v>78</v>
+      </c>
+      <c r="D16" s="12">
+        <v>1</v>
+      </c>
+      <c r="E16" s="13">
+        <v>0.11</v>
+      </c>
+      <c r="F16" s="9">
+        <v>0.11</v>
+      </c>
       <c r="G16" s="11"/>
-      <c r="H16" s="11"/>
+      <c r="H16" s="19" t="s">
+        <v>79</v>
+      </c>
       <c r="I16" s="11"/>
       <c r="J16" s="11"/>
     </row>
     <row r="17" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="11"/>
-      <c r="B17" s="11"/>
-      <c r="C17" s="11"/>
-      <c r="D17" s="12"/>
-      <c r="E17" s="13"/>
-      <c r="F17" s="9"/>
+      <c r="A17" s="18" t="s">
+        <v>71</v>
+      </c>
+      <c r="B17" s="11" t="s">
+        <v>72</v>
+      </c>
+      <c r="C17" s="11" t="s">
+        <v>73</v>
+      </c>
+      <c r="D17" s="12">
+        <v>4</v>
+      </c>
+      <c r="E17" s="13">
+        <v>0.04</v>
+      </c>
+      <c r="F17" s="9">
+        <v>0.16</v>
+      </c>
       <c r="G17" s="11"/>
-      <c r="H17" s="11"/>
+      <c r="H17" s="19" t="s">
+        <v>74</v>
+      </c>
       <c r="I17" s="11"/>
       <c r="J17" s="11"/>
     </row>
@@ -1125,7 +1267,7 @@
       </c>
       <c r="F20" s="5">
         <f>SUM(F2:F19)</f>
-        <v>259.20000000000005</v>
+        <v>266.87000000000012</v>
       </c>
     </row>
   </sheetData>
@@ -1146,8 +1288,11 @@
     <hyperlink ref="I4" r:id="rId13" xr:uid="{6767DCFE-C4EA-4F98-917F-25EE5BC81B62}"/>
     <hyperlink ref="H11" r:id="rId14" xr:uid="{7788AAC0-3264-469D-9FE8-88ABE62A1188}"/>
     <hyperlink ref="H12" r:id="rId15" xr:uid="{1563652D-3B5B-4137-B0DA-8740E4BAA28B}"/>
+    <hyperlink ref="H13" r:id="rId16" xr:uid="{F2E7CC8F-238C-4247-B8F0-EE48259CB0DF}"/>
+    <hyperlink ref="H14" r:id="rId17" xr:uid="{7CB04A90-A0AB-42C8-9E7C-D25B0500F1ED}"/>
+    <hyperlink ref="H17" r:id="rId18" xr:uid="{9716C910-2B10-4623-8055-2C5370BB167F}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId16"/>
+  <pageSetup orientation="portrait" r:id="rId19"/>
 </worksheet>
 </file>
--- a/accessories/cable-2/cable-2.xlsx
+++ b/accessories/cable-2/cable-2.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/4c0fa0fe96562a9e/Documents/GitHub/Battery-Lab-Hardware/accessories/cable-2/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="56" documentId="13_ncr:1_{8D074E32-F380-4A8B-BFB4-C9C0509B5722}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BC190208-072E-41E2-B21D-04C696366BAB}"/>
+  <xr:revisionPtr revIDLastSave="69" documentId="13_ncr:1_{8D074E32-F380-4A8B-BFB4-C9C0509B5722}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{18097E97-C9CB-4E42-AFA4-DABC874BB7BA}"/>
   <bookViews>
-    <workbookView xWindow="15480" yWindow="1080" windowWidth="3720" windowHeight="5527" xr2:uid="{FDAE7DA4-9528-4FC7-A320-70DA50473DCE}"/>
+    <workbookView xWindow="390" yWindow="390" windowWidth="21600" windowHeight="11055" xr2:uid="{FDAE7DA4-9528-4FC7-A320-70DA50473DCE}"/>
   </bookViews>
   <sheets>
     <sheet name="bill_of_materials" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="82" uniqueCount="80">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="72">
   <si>
     <t>Individual Cost</t>
   </si>
@@ -230,18 +230,6 @@
     <t>https://www.digikey.com/en/products/detail/anderson-power-products-inc/113899P1/10647423?s=N4IgTCBcDaIIxwMwA4CcqAKcQF0C%2BQA</t>
   </si>
   <si>
-    <t>HDW.BAG FOR SB/SBS50-HDL</t>
-  </si>
-  <si>
-    <t>104G17</t>
-  </si>
-  <si>
-    <t>https://www.digikey.com/en/products/detail/anderson-power-products-inc/104G17/14552097</t>
-  </si>
-  <si>
-    <t>SB50 Handle Screws</t>
-  </si>
-  <si>
     <t>Standard Socket Head Cap Screw: M3x0.50, 20 mm Lg, Low-Profile Std, Black Oxide, Alloy Steel, 50 PK</t>
   </si>
   <si>
@@ -263,19 +251,7 @@
     <t>https://www.grainger.com/product/Hex-Nut-Std-Hex-26KR85?searchQuery=M01300.030.0001&amp;searchBar=true&amp;tier=Tier+6&amp;suggestConfigId=6&amp;s_e=false</t>
   </si>
   <si>
-    <t>SBS75 Handle Screws Long</t>
-  </si>
-  <si>
-    <t>SBS75 Handle Screws Short</t>
-  </si>
-  <si>
-    <t>Standard Socket Head Cap Screw: M3x0.50, 18 mm Lg, Std, Black Oxide, Alloy Steel, Class 12.9, 100 PK</t>
-  </si>
-  <si>
-    <t>M07000.030.0018</t>
-  </si>
-  <si>
-    <t>https://www.grainger.com/product/Standard-Socket-Head-Cap-Screw-6CE54</t>
+    <t>SBS75 Handle Screws</t>
   </si>
 </sst>
 </file>
@@ -446,6 +422,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1147,103 +1127,75 @@
     </row>
     <row r="14" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="10" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="B14" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="C14" s="4" t="s">
+      <c r="C14" s="2" t="s">
         <v>65</v>
       </c>
       <c r="D14" s="2">
-        <v>2</v>
-      </c>
-      <c r="E14" s="9">
-        <v>1.97</v>
+        <v>4</v>
+      </c>
+      <c r="E14" s="8">
+        <v>0.37</v>
       </c>
       <c r="F14" s="9">
-        <v>3.94</v>
+        <v>1.48</v>
       </c>
       <c r="G14" s="5"/>
-      <c r="H14" s="1" t="s">
+      <c r="H14" s="3" t="s">
         <v>66</v>
       </c>
       <c r="I14" s="4"/>
     </row>
     <row r="15" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="10" t="s">
-        <v>75</v>
-      </c>
-      <c r="B15" s="2" t="s">
+      <c r="A15" s="18" t="s">
+        <v>67</v>
+      </c>
+      <c r="B15" s="11" t="s">
         <v>68</v>
       </c>
-      <c r="C15" s="2" t="s">
+      <c r="C15" s="11" t="s">
         <v>69</v>
       </c>
-      <c r="D15" s="2">
-        <v>2</v>
-      </c>
-      <c r="E15" s="8">
-        <v>0.37</v>
+      <c r="D15" s="12">
+        <v>4</v>
+      </c>
+      <c r="E15" s="13">
+        <v>0.04</v>
       </c>
       <c r="F15" s="9">
-        <v>0.74</v>
-      </c>
-      <c r="G15" s="5"/>
-      <c r="H15" s="3" t="s">
+        <v>0.16</v>
+      </c>
+      <c r="G15" s="11"/>
+      <c r="H15" s="19" t="s">
         <v>70</v>
       </c>
       <c r="I15" s="4"/>
     </row>
     <row r="16" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="10" t="s">
-        <v>76</v>
-      </c>
-      <c r="B16" s="11" t="s">
-        <v>77</v>
-      </c>
-      <c r="C16" s="11" t="s">
-        <v>78</v>
-      </c>
-      <c r="D16" s="12">
-        <v>1</v>
-      </c>
-      <c r="E16" s="13">
-        <v>0.11</v>
-      </c>
-      <c r="F16" s="9">
-        <v>0.11</v>
-      </c>
+      <c r="A16" s="18"/>
+      <c r="B16" s="11"/>
+      <c r="C16" s="11"/>
+      <c r="D16" s="12"/>
+      <c r="E16" s="13"/>
+      <c r="F16" s="9"/>
       <c r="G16" s="11"/>
-      <c r="H16" s="19" t="s">
-        <v>79</v>
-      </c>
+      <c r="H16" s="19"/>
       <c r="I16" s="11"/>
       <c r="J16" s="11"/>
     </row>
     <row r="17" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="18" t="s">
-        <v>71</v>
-      </c>
-      <c r="B17" s="11" t="s">
-        <v>72</v>
-      </c>
-      <c r="C17" s="11" t="s">
-        <v>73</v>
-      </c>
-      <c r="D17" s="12">
-        <v>4</v>
-      </c>
-      <c r="E17" s="13">
-        <v>0.04</v>
-      </c>
-      <c r="F17" s="9">
-        <v>0.16</v>
-      </c>
+      <c r="A17" s="18"/>
+      <c r="B17" s="11"/>
+      <c r="C17" s="11"/>
+      <c r="D17" s="12"/>
+      <c r="E17" s="13"/>
+      <c r="F17" s="9"/>
       <c r="G17" s="11"/>
-      <c r="H17" s="19" t="s">
-        <v>74</v>
-      </c>
+      <c r="H17" s="19"/>
       <c r="I17" s="11"/>
       <c r="J17" s="11"/>
     </row>
@@ -1267,7 +1219,7 @@
       </c>
       <c r="F20" s="5">
         <f>SUM(F2:F19)</f>
-        <v>266.87000000000012</v>
+        <v>263.56000000000012</v>
       </c>
     </row>
   </sheetData>
@@ -1289,10 +1241,9 @@
     <hyperlink ref="H11" r:id="rId14" xr:uid="{7788AAC0-3264-469D-9FE8-88ABE62A1188}"/>
     <hyperlink ref="H12" r:id="rId15" xr:uid="{1563652D-3B5B-4137-B0DA-8740E4BAA28B}"/>
     <hyperlink ref="H13" r:id="rId16" xr:uid="{F2E7CC8F-238C-4247-B8F0-EE48259CB0DF}"/>
-    <hyperlink ref="H14" r:id="rId17" xr:uid="{7CB04A90-A0AB-42C8-9E7C-D25B0500F1ED}"/>
-    <hyperlink ref="H17" r:id="rId18" xr:uid="{9716C910-2B10-4623-8055-2C5370BB167F}"/>
+    <hyperlink ref="H15" r:id="rId17" xr:uid="{22EA5B08-E3BF-44B7-9BC4-A52144A8B4E8}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId19"/>
+  <pageSetup orientation="portrait" r:id="rId18"/>
 </worksheet>
 </file>
--- a/accessories/cable-2/cable-2.xlsx
+++ b/accessories/cable-2/cable-2.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/4c0fa0fe96562a9e/Documents/GitHub/Battery-Lab-Hardware/accessories/cable-2/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\adowney2\Documents\GitHub\Battery-Lab-Hardware\accessories\cable-2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="69" documentId="13_ncr:1_{8D074E32-F380-4A8B-BFB4-C9C0509B5722}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{18097E97-C9CB-4E42-AFA4-DABC874BB7BA}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C8C1E71C-9A19-4E62-B64E-D0738A6A04E4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="390" yWindow="390" windowWidth="21600" windowHeight="11055" xr2:uid="{FDAE7DA4-9528-4FC7-A320-70DA50473DCE}"/>
+    <workbookView xWindow="-16320" yWindow="-6540" windowWidth="16440" windowHeight="28320" xr2:uid="{FDAE7DA4-9528-4FC7-A320-70DA50473DCE}"/>
   </bookViews>
   <sheets>
     <sheet name="bill_of_materials" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="72">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="74">
   <si>
     <t>Individual Cost</t>
   </si>
@@ -209,15 +209,6 @@
     <t>https://www.digikey.com/en/products/detail/qualtek/Q5-2X-3-4-01-QB48IN-5/754962</t>
   </si>
   <si>
-    <t>Adhesive Lined heat shrink</t>
-  </si>
-  <si>
-    <t>HEATSHRINK 0.752" X 4' BLK 1=1PC</t>
-  </si>
-  <si>
-    <t>Q5-2X-3/4-01-QB48IN-5</t>
-  </si>
-  <si>
     <t xml:space="preserve">SB50/120 T Handle </t>
   </si>
   <si>
@@ -252,6 +243,21 @@
   </si>
   <si>
     <t>SBS75 Handle Screws</t>
+  </si>
+  <si>
+    <t>3/4 in Heat Shrink Tubing</t>
+  </si>
+  <si>
+    <t>SHRINK-KON Heat Shrink Tubing: 0.75 in I.D. Before Shrinking, 0.38 in I.D. After Shrinking, 10 PK</t>
+  </si>
+  <si>
+    <t>CPO75006</t>
+  </si>
+  <si>
+    <t>2:1 shrink, black, 10-pack</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.grainger.com/product/SHRINK-KON-Heat-Shrink-Tubing-0-75-in-3KH60 </t>
   </si>
 </sst>
 </file>
@@ -298,11 +304,13 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="10"/>
       <name val="Aptos Narrow"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="9"/>
@@ -349,7 +357,7 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -404,6 +412,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
+    <xf numFmtId="8" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -422,10 +431,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -745,7 +750,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C6D3A36C-E8CE-4E50-A172-E48E2F9A45A8}">
-  <dimension ref="A1:M20"/>
+  <dimension ref="A1:M19"/>
   <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="22.28515625" customWidth="1"/>
@@ -1013,7 +1018,7 @@
         <v>2.4</v>
       </c>
       <c r="F9" s="9">
-        <f t="shared" ref="F9:F12" si="1">D9*E9</f>
+        <f t="shared" ref="F9:F11" si="1">D9*E9</f>
         <v>4.8</v>
       </c>
       <c r="G9" s="5"/>
@@ -1087,22 +1092,21 @@
       <c r="D12" s="2">
         <v>1</v>
       </c>
-      <c r="E12" s="9">
-        <v>6.22</v>
+      <c r="E12" s="8">
+        <v>2.72</v>
       </c>
       <c r="F12" s="9">
-        <f t="shared" si="1"/>
-        <v>6.22</v>
+        <v>2.72</v>
       </c>
       <c r="G12" s="5"/>
-      <c r="H12" s="1" t="s">
-        <v>56</v>
+      <c r="H12" s="3" t="s">
+        <v>60</v>
       </c>
       <c r="I12" s="4"/>
     </row>
     <row r="13" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="10" t="s">
-        <v>60</v>
+        <v>68</v>
       </c>
       <c r="B13" s="2" t="s">
         <v>61</v>
@@ -1111,13 +1115,13 @@
         <v>62</v>
       </c>
       <c r="D13" s="2">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E13" s="8">
-        <v>2.72</v>
+        <v>0.37</v>
       </c>
       <c r="F13" s="9">
-        <v>2.72</v>
+        <v>1.48</v>
       </c>
       <c r="G13" s="5"/>
       <c r="H13" s="3" t="s">
@@ -1126,54 +1130,59 @@
       <c r="I13" s="4"/>
     </row>
     <row r="14" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="10" t="s">
+      <c r="A14" s="18" t="s">
+        <v>64</v>
+      </c>
+      <c r="B14" s="11" t="s">
+        <v>65</v>
+      </c>
+      <c r="C14" s="11" t="s">
+        <v>66</v>
+      </c>
+      <c r="D14" s="12">
+        <v>4</v>
+      </c>
+      <c r="E14" s="13">
+        <v>0.04</v>
+      </c>
+      <c r="F14" s="9">
+        <v>0.16</v>
+      </c>
+      <c r="G14" s="11"/>
+      <c r="H14" s="19" t="s">
+        <v>67</v>
+      </c>
+      <c r="I14" s="4"/>
+    </row>
+    <row r="15" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>69</v>
+      </c>
+      <c r="B15" t="s">
+        <v>70</v>
+      </c>
+      <c r="C15" t="s">
         <v>71</v>
       </c>
-      <c r="B14" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="C14" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="D14" s="2">
-        <v>4</v>
-      </c>
-      <c r="E14" s="8">
-        <v>0.37</v>
-      </c>
-      <c r="F14" s="9">
-        <v>1.48</v>
-      </c>
-      <c r="G14" s="5"/>
-      <c r="H14" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="I14" s="4"/>
-    </row>
-    <row r="15" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="18" t="s">
-        <v>67</v>
-      </c>
-      <c r="B15" s="11" t="s">
-        <v>68</v>
-      </c>
-      <c r="C15" s="11" t="s">
-        <v>69</v>
-      </c>
-      <c r="D15" s="12">
-        <v>4</v>
-      </c>
-      <c r="E15" s="13">
-        <v>0.04</v>
-      </c>
-      <c r="F15" s="9">
-        <v>0.16</v>
-      </c>
-      <c r="G15" s="11"/>
-      <c r="H15" s="19" t="s">
-        <v>70</v>
-      </c>
-      <c r="I15" s="4"/>
+      <c r="D15">
+        <v>1</v>
+      </c>
+      <c r="E15" s="20">
+        <v>5.14</v>
+      </c>
+      <c r="F15" s="20">
+        <v>5.14</v>
+      </c>
+      <c r="G15" t="s">
+        <v>72</v>
+      </c>
+      <c r="H15" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="I15" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="J15" s="11"/>
     </row>
     <row r="16" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="18"/>
@@ -1187,39 +1196,27 @@
       <c r="I16" s="11"/>
       <c r="J16" s="11"/>
     </row>
-    <row r="17" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="18"/>
-      <c r="B17" s="11"/>
-      <c r="C17" s="11"/>
-      <c r="D17" s="12"/>
-      <c r="E17" s="13"/>
-      <c r="F17" s="9"/>
-      <c r="G17" s="11"/>
-      <c r="H17" s="19"/>
-      <c r="I17" s="11"/>
-      <c r="J17" s="11"/>
-    </row>
-    <row r="18" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="4"/>
-      <c r="B18" s="4"/>
-      <c r="C18" s="14"/>
-      <c r="D18" s="14"/>
-      <c r="E18" s="15"/>
-      <c r="F18" s="15"/>
-      <c r="G18" s="4"/>
-      <c r="H18" s="4"/>
-    </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="E19" s="8"/>
-      <c r="F19" s="8"/>
-    </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="E20" s="7" t="s">
+    <row r="17" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="4"/>
+      <c r="B17" s="4"/>
+      <c r="C17" s="14"/>
+      <c r="D17" s="14"/>
+      <c r="E17" s="15"/>
+      <c r="F17" s="15"/>
+      <c r="G17" s="4"/>
+      <c r="H17" s="4"/>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="E18" s="8"/>
+      <c r="F18" s="8"/>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="E19" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="F20" s="5">
-        <f>SUM(F2:F19)</f>
-        <v>263.56000000000012</v>
+      <c r="F19" s="5">
+        <f>SUM(F2:F18)</f>
+        <v>262.48</v>
       </c>
     </row>
   </sheetData>
@@ -1239,11 +1236,12 @@
     <hyperlink ref="I3" r:id="rId12" xr:uid="{2F4C748B-C31C-4C18-98A1-F896819BEDE6}"/>
     <hyperlink ref="I4" r:id="rId13" xr:uid="{6767DCFE-C4EA-4F98-917F-25EE5BC81B62}"/>
     <hyperlink ref="H11" r:id="rId14" xr:uid="{7788AAC0-3264-469D-9FE8-88ABE62A1188}"/>
-    <hyperlink ref="H12" r:id="rId15" xr:uid="{1563652D-3B5B-4137-B0DA-8740E4BAA28B}"/>
-    <hyperlink ref="H13" r:id="rId16" xr:uid="{F2E7CC8F-238C-4247-B8F0-EE48259CB0DF}"/>
-    <hyperlink ref="H15" r:id="rId17" xr:uid="{22EA5B08-E3BF-44B7-9BC4-A52144A8B4E8}"/>
+    <hyperlink ref="I15" r:id="rId15" xr:uid="{1563652D-3B5B-4137-B0DA-8740E4BAA28B}"/>
+    <hyperlink ref="H12" r:id="rId16" xr:uid="{F2E7CC8F-238C-4247-B8F0-EE48259CB0DF}"/>
+    <hyperlink ref="H14" r:id="rId17" xr:uid="{22EA5B08-E3BF-44B7-9BC4-A52144A8B4E8}"/>
+    <hyperlink ref="H15" r:id="rId18" xr:uid="{F793E78D-40BD-4333-BDA2-FAA984605D18}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId18"/>
+  <pageSetup orientation="portrait" r:id="rId19"/>
 </worksheet>
 </file>